--- a/_data/characters.xlsx
+++ b/_data/characters.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Aide" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Apparitions!$A$1:$G$871</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Apparitions!$A$1:$G$870</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Personnages!$A$1:$H$412</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5349" uniqueCount="1988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5346" uniqueCount="1988">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -5588,12 +5588,21 @@
     <t xml:space="preserve">2017-2021</t>
   </si>
   <si>
+    <t xml:space="preserve">Auntie Edna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibles 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary Poppins Returns</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ralph Breaks the Internet</t>
   </si>
   <si>
-    <t xml:space="preserve">2018</t>
-  </si>
-  <si>
     <t xml:space="preserve">BuzzLightyear2018.png</t>
   </si>
   <si>
@@ -5637,15 +5646,6 @@
   </si>
   <si>
     <t xml:space="preserve">Calhoun2018.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auntie Edna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibles 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary Poppins Returns</t>
   </si>
   <si>
     <t xml:space="preserve">SnowWhite2018.png</t>
@@ -17468,7 +17468,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1871"/>
+  <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -25307,8 +25307,8 @@
       <c r="F605" s="5"/>
     </row>
     <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A606" s="6" t="s">
-        <v>606</v>
+      <c r="A606" s="4" t="s">
+        <v>946</v>
       </c>
       <c r="B606" s="1" t="s">
         <v>1849</v>
@@ -25316,287 +25316,290 @@
       <c r="C606" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="E606" s="1" t="s">
+      <c r="F606" s="5"/>
+    </row>
+    <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A607" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="B607" s="1" t="s">
         <v>1851</v>
-      </c>
-    </row>
-    <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A607" s="6" t="s">
-        <v>1415</v>
-      </c>
-      <c r="B607" s="1" t="s">
-        <v>1849</v>
       </c>
       <c r="C607" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="E607" s="1" t="s">
-        <v>1852</v>
-      </c>
+      <c r="F607" s="5"/>
     </row>
     <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A608" s="6" t="s">
-        <v>1436</v>
+      <c r="A608" s="4" t="s">
+        <v>936</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="C608" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="E608" s="1" t="s">
-        <v>1853</v>
-      </c>
+      <c r="F608" s="5"/>
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A609" s="6" t="s">
-        <v>1439</v>
+      <c r="A609" s="4" t="s">
+        <v>946</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="C609" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="E609" s="1" t="s">
-        <v>1854</v>
-      </c>
+      <c r="F609" s="5"/>
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A610" s="6" t="s">
-        <v>1458</v>
+      <c r="A610" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="C610" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="E610" s="1" t="s">
-        <v>1855</v>
-      </c>
+      <c r="F610" s="5"/>
     </row>
     <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A611" s="6" t="s">
-        <v>37</v>
+      <c r="A611" s="4" t="s">
+        <v>269</v>
       </c>
       <c r="B611" s="1" t="s">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="C611" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="E611" s="1" t="s">
-        <v>1856</v>
-      </c>
+      <c r="F611" s="5"/>
     </row>
     <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A612" s="6" t="s">
-        <v>1506</v>
+        <v>606</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C612" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A613" s="6" t="s">
-        <v>1527</v>
+        <v>1415</v>
       </c>
       <c r="B613" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C613" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A614" s="6" t="s">
-        <v>1539</v>
+        <v>1436</v>
       </c>
       <c r="B614" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C614" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E614" s="1" t="s">
-        <v>1859</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A615" s="6" t="s">
-        <v>1542</v>
+        <v>1439</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C615" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="6" t="s">
-        <v>1554</v>
+        <v>1458</v>
       </c>
       <c r="B616" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C616" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E616" s="1" t="s">
-        <v>1861</v>
-      </c>
-      <c r="F616" s="1" t="n">
-        <v>4</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A617" s="6" t="s">
-        <v>1560</v>
+        <v>37</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C617" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E617" s="1" t="s">
-        <v>1862</v>
+        <v>1859</v>
+      </c>
+      <c r="G617" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="6" t="s">
-        <v>1563</v>
+        <v>1506</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C618" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E618" s="1" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="6" t="s">
-        <v>1575</v>
+        <v>1527</v>
       </c>
       <c r="B619" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C619" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E619" s="1" t="s">
-        <v>1864</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="6" t="s">
-        <v>1578</v>
+        <v>1539</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C620" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E620" s="1" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A621" s="4" t="s">
-        <v>946</v>
+      <c r="A621" s="6" t="s">
+        <v>1542</v>
       </c>
       <c r="B621" s="1" t="s">
-        <v>1866</v>
+        <v>1853</v>
       </c>
       <c r="C621" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="F621" s="5"/>
+      <c r="E621" s="1" t="s">
+        <v>1863</v>
+      </c>
     </row>
     <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A622" s="4" t="s">
-        <v>930</v>
+      <c r="A622" s="6" t="s">
+        <v>1554</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>1867</v>
+        <v>1853</v>
       </c>
       <c r="C622" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="F622" s="5"/>
+      <c r="E622" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F622" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A623" s="4" t="s">
-        <v>936</v>
+      <c r="A623" s="6" t="s">
+        <v>1560</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>1867</v>
+        <v>1853</v>
       </c>
       <c r="C623" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="F623" s="5"/>
+      <c r="E623" s="1" t="s">
+        <v>1865</v>
+      </c>
     </row>
     <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A624" s="4" t="s">
-        <v>946</v>
+      <c r="A624" s="6" t="s">
+        <v>1563</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>1867</v>
+        <v>1853</v>
       </c>
       <c r="C624" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="F624" s="5"/>
+      <c r="E624" s="1" t="s">
+        <v>1866</v>
+      </c>
     </row>
     <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A625" s="4" t="s">
-        <v>258</v>
+      <c r="A625" s="6" t="s">
+        <v>1575</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>1868</v>
+        <v>1853</v>
       </c>
       <c r="C625" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="F625" s="5"/>
+      <c r="E625" s="1" t="s">
+        <v>1867</v>
+      </c>
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A626" s="4" t="s">
-        <v>269</v>
+      <c r="A626" s="6" t="s">
+        <v>1578</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>1868</v>
+        <v>1853</v>
       </c>
       <c r="C626" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="F626" s="5"/>
+      <c r="E626" s="1" t="s">
+        <v>1868</v>
+      </c>
     </row>
     <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B627" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C627" s="10" t="s">
         <v>1850</v>
@@ -25608,307 +25611,304 @@
     </row>
     <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A628" s="4" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="B628" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C628" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E628" s="1" t="s">
-        <v>1856</v>
+        <v>1870</v>
       </c>
       <c r="F628" s="5"/>
     </row>
     <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A629" s="4" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="B629" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C629" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E629" s="1" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="F629" s="5"/>
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="4" t="s">
-        <v>197</v>
+        <v>426</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C630" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E630" s="1" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="F630" s="5"/>
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="4" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C631" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E631" s="1" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="F631" s="5"/>
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="4" t="s">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C632" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E632" s="1" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="F632" s="5"/>
     </row>
     <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A633" s="4" t="s">
-        <v>502</v>
+        <v>582</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C633" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E633" s="1" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="F633" s="5"/>
     </row>
     <row r="634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A634" s="4" t="s">
-        <v>582</v>
+        <v>723</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C634" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E634" s="1" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="F634" s="5"/>
     </row>
     <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A635" s="4" t="s">
-        <v>723</v>
+        <v>1001</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C635" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E635" s="1" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="F635" s="5"/>
     </row>
     <row r="636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A636" s="4" t="s">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C636" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E636" s="1" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F636" s="5"/>
     </row>
     <row r="637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A637" s="4" t="s">
-        <v>1026</v>
+        <v>1053</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C637" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E637" s="1" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="F637" s="5"/>
     </row>
     <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A638" s="4" t="s">
-        <v>1053</v>
+        <v>1078</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C638" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E638" s="1" t="s">
-        <v>1879</v>
-      </c>
-      <c r="F638" s="5"/>
+        <v>1880</v>
+      </c>
+      <c r="F638" s="5" t="s">
+        <v>1719</v>
+      </c>
     </row>
     <row r="639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A639" s="4" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C639" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E639" s="1" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="F639" s="5" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="640" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A640" s="4" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C640" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="F640" s="5" t="s">
-        <v>1718</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="641" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="4" t="s">
-        <v>1090</v>
+        <v>1103</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C641" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E641" s="1" t="s">
-        <v>1882</v>
-      </c>
-      <c r="F641" s="5" t="s">
-        <v>1791</v>
-      </c>
+        <v>1883</v>
+      </c>
+      <c r="F641" s="5"/>
     </row>
     <row r="642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A642" s="4" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C642" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E642" s="1" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="F642" s="5"/>
     </row>
     <row r="643" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A643" s="4" t="s">
-        <v>1108</v>
+        <v>1190</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C643" s="10" t="s">
         <v>1850</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="F643" s="5"/>
     </row>
     <row r="644" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A644" s="4" t="s">
-        <v>1190</v>
+        <v>1448</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>1849</v>
-      </c>
-      <c r="C644" s="10" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C644" s="5" t="s">
         <v>1850</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="F644" s="5"/>
     </row>
     <row r="645" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="4" t="s">
-        <v>1448</v>
+        <v>1236</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1849</v>
+        <v>1239</v>
       </c>
       <c r="C645" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="E645" s="1" t="s">
-        <v>1886</v>
-      </c>
       <c r="F645" s="5"/>
     </row>
     <row r="646" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A646" s="4" t="s">
-        <v>1236</v>
+        <v>1185</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1239</v>
+        <v>1887</v>
       </c>
       <c r="C646" s="5" t="s">
-        <v>1850</v>
+        <v>1888</v>
       </c>
       <c r="F646" s="5"/>
     </row>
     <row r="647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A647" s="4" t="s">
-        <v>1185</v>
+        <v>498</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="C647" s="5" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="F647" s="5"/>
     </row>
     <row r="648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A648" s="4" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B648" s="1" t="s">
         <v>1889</v>
@@ -25920,7 +25920,7 @@
     </row>
     <row r="649" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A649" s="4" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B649" s="1" t="s">
         <v>1889</v>
@@ -25932,7 +25932,7 @@
     </row>
     <row r="650" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A650" s="4" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B650" s="1" t="s">
         <v>1889</v>
@@ -25944,7 +25944,7 @@
     </row>
     <row r="651" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A651" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B651" s="1" t="s">
         <v>1889</v>
@@ -25956,19 +25956,24 @@
     </row>
     <row r="652" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A652" s="4" t="s">
-        <v>514</v>
+        <v>1103</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="C652" s="5" t="s">
         <v>1890</v>
       </c>
-      <c r="F652" s="5"/>
+      <c r="D652" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F652" s="5" t="s">
+        <v>1719</v>
+      </c>
     </row>
     <row r="653" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A653" s="4" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="B653" s="1" t="s">
         <v>1891</v>
@@ -25980,12 +25985,12 @@
         <v>1892</v>
       </c>
       <c r="F653" s="5" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="654" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A654" s="4" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="B654" s="1" t="s">
         <v>1891</v>
@@ -25997,12 +26002,12 @@
         <v>1892</v>
       </c>
       <c r="F654" s="5" t="s">
-        <v>1718</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="655" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A655" s="4" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="B655" s="1" t="s">
         <v>1891</v>
@@ -26013,13 +26018,11 @@
       <c r="D655" s="1" t="s">
         <v>1892</v>
       </c>
-      <c r="F655" s="5" t="s">
-        <v>1791</v>
-      </c>
+      <c r="F655" s="5"/>
     </row>
     <row r="656" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A656" s="4" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="B656" s="1" t="s">
         <v>1891</v>
@@ -26030,11 +26033,13 @@
       <c r="D656" s="1" t="s">
         <v>1892</v>
       </c>
-      <c r="F656" s="5"/>
+      <c r="F656" s="5" t="s">
+        <v>1792</v>
+      </c>
     </row>
     <row r="657" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A657" s="4" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="B657" s="1" t="s">
         <v>1891</v>
@@ -26046,29 +26051,24 @@
         <v>1892</v>
       </c>
       <c r="F657" s="5" t="s">
-        <v>1792</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="658" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A658" s="4" t="s">
-        <v>1124</v>
+        <v>173</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="C658" s="5" t="s">
         <v>1890</v>
       </c>
-      <c r="D658" s="1" t="s">
-        <v>1892</v>
-      </c>
-      <c r="F658" s="5" t="s">
-        <v>1893</v>
-      </c>
+      <c r="F658" s="5"/>
     </row>
     <row r="659" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A659" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B659" s="1" t="s">
         <v>1894</v>
@@ -26080,7 +26080,7 @@
     </row>
     <row r="660" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A660" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B660" s="1" t="s">
         <v>1894</v>
@@ -26092,7 +26092,7 @@
     </row>
     <row r="661" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A661" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B661" s="1" t="s">
         <v>1894</v>
@@ -26104,7 +26104,7 @@
     </row>
     <row r="662" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A662" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B662" s="1" t="s">
         <v>1894</v>
@@ -26116,7 +26116,7 @@
     </row>
     <row r="663" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A663" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B663" s="1" t="s">
         <v>1894</v>
@@ -26128,10 +26128,10 @@
     </row>
     <row r="664" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A664" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="C664" s="5" t="s">
         <v>1890</v>
@@ -26140,7 +26140,7 @@
     </row>
     <row r="665" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A665" s="4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B665" s="1" t="s">
         <v>1895</v>
@@ -26152,7 +26152,7 @@
     </row>
     <row r="666" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A666" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B666" s="1" t="s">
         <v>1895</v>
@@ -26164,7 +26164,7 @@
     </row>
     <row r="667" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A667" s="4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B667" s="1" t="s">
         <v>1895</v>
@@ -26176,19 +26176,22 @@
     </row>
     <row r="668" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A668" s="4" t="s">
-        <v>212</v>
+        <v>538</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C668" s="5" t="s">
         <v>1890</v>
       </c>
+      <c r="E668" s="1" t="s">
+        <v>1897</v>
+      </c>
       <c r="F668" s="5"/>
     </row>
     <row r="669" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A669" s="4" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B669" s="1" t="s">
         <v>1896</v>
@@ -26197,13 +26200,13 @@
         <v>1890</v>
       </c>
       <c r="E669" s="1" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="F669" s="5"/>
     </row>
     <row r="670" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A670" s="4" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B670" s="1" t="s">
         <v>1896</v>
@@ -26212,13 +26215,13 @@
         <v>1890</v>
       </c>
       <c r="E670" s="1" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="F670" s="5"/>
     </row>
     <row r="671" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A671" s="4" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B671" s="1" t="s">
         <v>1896</v>
@@ -26227,13 +26230,13 @@
         <v>1890</v>
       </c>
       <c r="E671" s="1" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="F671" s="5"/>
     </row>
     <row r="672" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A672" s="4" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B672" s="1" t="s">
         <v>1896</v>
@@ -26242,13 +26245,13 @@
         <v>1890</v>
       </c>
       <c r="E672" s="1" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="F672" s="5"/>
     </row>
     <row r="673" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A673" s="4" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B673" s="1" t="s">
         <v>1896</v>
@@ -26257,13 +26260,13 @@
         <v>1890</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="F673" s="5"/>
     </row>
     <row r="674" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A674" s="4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B674" s="1" t="s">
         <v>1896</v>
@@ -26272,28 +26275,25 @@
         <v>1890</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="F674" s="5"/>
     </row>
     <row r="675" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A675" s="4" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1896</v>
+        <v>1904</v>
       </c>
       <c r="C675" s="5" t="s">
         <v>1890</v>
       </c>
-      <c r="E675" s="1" t="s">
-        <v>1903</v>
-      </c>
       <c r="F675" s="5"/>
     </row>
     <row r="676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A676" s="4" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B676" s="1" t="s">
         <v>1904</v>
@@ -26305,7 +26305,7 @@
     </row>
     <row r="677" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A677" s="4" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B677" s="1" t="s">
         <v>1904</v>
@@ -26317,7 +26317,7 @@
     </row>
     <row r="678" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A678" s="4" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B678" s="1" t="s">
         <v>1904</v>
@@ -26329,7 +26329,7 @@
     </row>
     <row r="679" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A679" s="4" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B679" s="1" t="s">
         <v>1904</v>
@@ -26341,7 +26341,7 @@
     </row>
     <row r="680" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A680" s="4" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B680" s="1" t="s">
         <v>1904</v>
@@ -26353,7 +26353,7 @@
     </row>
     <row r="681" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A681" s="4" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B681" s="1" t="s">
         <v>1904</v>
@@ -26365,7 +26365,7 @@
     </row>
     <row r="682" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A682" s="4" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B682" s="1" t="s">
         <v>1904</v>
@@ -26377,19 +26377,19 @@
     </row>
     <row r="683" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A683" s="4" t="s">
-        <v>626</v>
+        <v>601</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="C683" s="5" t="s">
-        <v>1890</v>
+        <v>1906</v>
       </c>
       <c r="F683" s="5"/>
     </row>
     <row r="684" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A684" s="4" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="B684" s="1" t="s">
         <v>1905</v>
@@ -26401,19 +26401,22 @@
     </row>
     <row r="685" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A685" s="4" t="s">
-        <v>626</v>
+        <v>723</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="C685" s="5" t="s">
         <v>1906</v>
       </c>
+      <c r="E685" s="1" t="s">
+        <v>1908</v>
+      </c>
       <c r="F685" s="5"/>
     </row>
     <row r="686" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A686" s="4" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
       <c r="B686" s="1" t="s">
         <v>1907</v>
@@ -26421,14 +26424,11 @@
       <c r="C686" s="5" t="s">
         <v>1906</v>
       </c>
-      <c r="E686" s="1" t="s">
-        <v>1908</v>
-      </c>
       <c r="F686" s="5"/>
     </row>
     <row r="687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A687" s="4" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="B687" s="1" t="s">
         <v>1907</v>
@@ -26440,10 +26440,10 @@
     </row>
     <row r="688" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A688" s="4" t="s">
-        <v>748</v>
+        <v>1120</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C688" s="5" t="s">
         <v>1906</v>
@@ -26452,10 +26452,10 @@
     </row>
     <row r="689" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A689" s="4" t="s">
-        <v>1120</v>
+        <v>1241</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1909</v>
+        <v>1244</v>
       </c>
       <c r="C689" s="5" t="s">
         <v>1906</v>
@@ -26464,7 +26464,7 @@
     </row>
     <row r="690" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A690" s="4" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="B690" s="1" t="s">
         <v>1244</v>
@@ -26476,10 +26476,10 @@
     </row>
     <row r="691" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A691" s="4" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="C691" s="5" t="s">
         <v>1906</v>
@@ -26488,7 +26488,7 @@
     </row>
     <row r="692" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A692" s="4" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="B692" s="1" t="s">
         <v>1251</v>
@@ -26500,10 +26500,10 @@
     </row>
     <row r="693" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A693" s="4" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1251</v>
+        <v>1260</v>
       </c>
       <c r="C693" s="5" t="s">
         <v>1906</v>
@@ -26512,7 +26512,7 @@
     </row>
     <row r="694" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A694" s="4" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="B694" s="1" t="s">
         <v>1260</v>
@@ -26524,10 +26524,10 @@
     </row>
     <row r="695" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A695" s="4" t="s">
-        <v>1262</v>
+        <v>435</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1260</v>
+        <v>1910</v>
       </c>
       <c r="C695" s="5" t="s">
         <v>1906</v>
@@ -26536,34 +26536,34 @@
     </row>
     <row r="696" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A696" s="4" t="s">
-        <v>435</v>
+        <v>8</v>
       </c>
       <c r="B696" s="1" t="s">
         <v>1910</v>
       </c>
       <c r="C696" s="5" t="s">
-        <v>1906</v>
+        <v>1911</v>
       </c>
       <c r="F696" s="5"/>
     </row>
     <row r="697" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A697" s="4" t="s">
-        <v>8</v>
+        <v>1262</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="C697" s="5" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="F697" s="5"/>
     </row>
     <row r="698" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A698" s="4" t="s">
-        <v>1262</v>
+        <v>223</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="C698" s="5" t="s">
         <v>1913</v>
@@ -26572,7 +26572,7 @@
     </row>
     <row r="699" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A699" s="4" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B699" s="1" t="s">
         <v>1914</v>
@@ -26584,7 +26584,7 @@
     </row>
     <row r="700" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A700" s="4" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B700" s="1" t="s">
         <v>1914</v>
@@ -26596,10 +26596,10 @@
     </row>
     <row r="701" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A701" s="4" t="s">
-        <v>240</v>
+        <v>1288</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>1914</v>
+        <v>1291</v>
       </c>
       <c r="C701" s="5" t="s">
         <v>1913</v>
@@ -26608,7 +26608,7 @@
     </row>
     <row r="702" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A702" s="4" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="B702" s="1" t="s">
         <v>1291</v>
@@ -26620,7 +26620,7 @@
     </row>
     <row r="703" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A703" s="4" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="B703" s="1" t="s">
         <v>1291</v>
@@ -26632,7 +26632,7 @@
     </row>
     <row r="704" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A704" s="4" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="B704" s="1" t="s">
         <v>1291</v>
@@ -26644,7 +26644,7 @@
     </row>
     <row r="705" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A705" s="4" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="B705" s="1" t="s">
         <v>1291</v>
@@ -26656,7 +26656,7 @@
     </row>
     <row r="706" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A706" s="4" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="B706" s="1" t="s">
         <v>1291</v>
@@ -26668,10 +26668,10 @@
     </row>
     <row r="707" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A707" s="4" t="s">
-        <v>1309</v>
+        <v>1279</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>1291</v>
+        <v>1280</v>
       </c>
       <c r="C707" s="5" t="s">
         <v>1913</v>
@@ -26680,7 +26680,7 @@
     </row>
     <row r="708" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A708" s="4" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="B708" s="1" t="s">
         <v>1280</v>
@@ -26692,7 +26692,7 @@
     </row>
     <row r="709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A709" s="4" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="B709" s="1" t="s">
         <v>1280</v>
@@ -26704,10 +26704,10 @@
     </row>
     <row r="710" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A710" s="4" t="s">
-        <v>1285</v>
+        <v>1120</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>1280</v>
+        <v>1915</v>
       </c>
       <c r="C710" s="5" t="s">
         <v>1913</v>
@@ -26716,10 +26716,10 @@
     </row>
     <row r="711" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A711" s="4" t="s">
-        <v>1120</v>
+        <v>1264</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>1915</v>
+        <v>1267</v>
       </c>
       <c r="C711" s="5" t="s">
         <v>1913</v>
@@ -26728,7 +26728,7 @@
     </row>
     <row r="712" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A712" s="4" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="B712" s="1" t="s">
         <v>1267</v>
@@ -26740,7 +26740,7 @@
     </row>
     <row r="713" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A713" s="4" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="B713" s="1" t="s">
         <v>1267</v>
@@ -26752,7 +26752,7 @@
     </row>
     <row r="714" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A714" s="4" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B714" s="1" t="s">
         <v>1267</v>
@@ -26764,19 +26764,22 @@
     </row>
     <row r="715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A715" s="4" t="s">
-        <v>1276</v>
+        <v>1128</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>1267</v>
+        <v>1916</v>
       </c>
       <c r="C715" s="5" t="s">
-        <v>1913</v>
+        <v>1917</v>
       </c>
       <c r="F715" s="5"/>
+      <c r="G715" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="716" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A716" s="4" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="B716" s="1" t="s">
         <v>1916</v>
@@ -26791,7 +26794,7 @@
     </row>
     <row r="717" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A717" s="4" t="s">
-        <v>1133</v>
+        <v>1144</v>
       </c>
       <c r="B717" s="1" t="s">
         <v>1916</v>
@@ -26806,22 +26809,19 @@
     </row>
     <row r="718" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A718" s="4" t="s">
-        <v>1144</v>
+        <v>954</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="C718" s="5" t="s">
         <v>1917</v>
       </c>
       <c r="F718" s="5"/>
-      <c r="G718" s="1" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="719" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A719" s="4" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="B719" s="1" t="s">
         <v>1918</v>
@@ -26833,7 +26833,7 @@
     </row>
     <row r="720" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A720" s="4" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B720" s="1" t="s">
         <v>1918</v>
@@ -26845,7 +26845,7 @@
     </row>
     <row r="721" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A721" s="4" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B721" s="1" t="s">
         <v>1918</v>
@@ -26857,7 +26857,7 @@
     </row>
     <row r="722" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A722" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="B722" s="1" t="s">
         <v>1918</v>
@@ -26869,7 +26869,7 @@
     </row>
     <row r="723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A723" s="4" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="B723" s="1" t="s">
         <v>1918</v>
@@ -26881,10 +26881,10 @@
     </row>
     <row r="724" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A724" s="4" t="s">
-        <v>979</v>
+        <v>64</v>
       </c>
       <c r="B724" s="1" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="C724" s="5" t="s">
         <v>1917</v>
@@ -26893,7 +26893,7 @@
     </row>
     <row r="725" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A725" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B725" s="1" t="s">
         <v>1919</v>
@@ -26905,7 +26905,7 @@
     </row>
     <row r="726" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A726" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B726" s="1" t="s">
         <v>1919</v>
@@ -26917,7 +26917,7 @@
     </row>
     <row r="727" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A727" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B727" s="1" t="s">
         <v>1919</v>
@@ -26929,7 +26929,7 @@
     </row>
     <row r="728" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A728" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B728" s="1" t="s">
         <v>1919</v>
@@ -26941,7 +26941,7 @@
     </row>
     <row r="729" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A729" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B729" s="1" t="s">
         <v>1919</v>
@@ -26953,10 +26953,10 @@
     </row>
     <row r="730" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A730" s="4" t="s">
-        <v>84</v>
+        <v>1313</v>
       </c>
       <c r="B730" s="1" t="s">
-        <v>1919</v>
+        <v>1316</v>
       </c>
       <c r="C730" s="5" t="s">
         <v>1917</v>
@@ -26965,7 +26965,7 @@
     </row>
     <row r="731" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A731" s="4" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="B731" s="1" t="s">
         <v>1316</v>
@@ -26977,7 +26977,7 @@
     </row>
     <row r="732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A732" s="4" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="B732" s="1" t="s">
         <v>1316</v>
@@ -26989,19 +26989,19 @@
     </row>
     <row r="733" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A733" s="4" t="s">
-        <v>1322</v>
+        <v>14</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>1316</v>
+        <v>1920</v>
       </c>
       <c r="C733" s="5" t="s">
-        <v>1917</v>
+        <v>1921</v>
       </c>
       <c r="F733" s="5"/>
     </row>
     <row r="734" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A734" s="4" t="s">
-        <v>14</v>
+        <v>426</v>
       </c>
       <c r="B734" s="1" t="s">
         <v>1920</v>
@@ -27013,7 +27013,7 @@
     </row>
     <row r="735" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A735" s="4" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="B735" s="1" t="s">
         <v>1920</v>
@@ -27025,7 +27025,7 @@
     </row>
     <row r="736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A736" s="4" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="B736" s="1" t="s">
         <v>1920</v>
@@ -27037,7 +27037,7 @@
     </row>
     <row r="737" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A737" s="4" t="s">
-        <v>472</v>
+        <v>1001</v>
       </c>
       <c r="B737" s="1" t="s">
         <v>1920</v>
@@ -27049,7 +27049,7 @@
     </row>
     <row r="738" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A738" s="4" t="s">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="B738" s="1" t="s">
         <v>1920</v>
@@ -27061,7 +27061,7 @@
     </row>
     <row r="739" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A739" s="4" t="s">
-        <v>1026</v>
+        <v>1190</v>
       </c>
       <c r="B739" s="1" t="s">
         <v>1920</v>
@@ -27073,10 +27073,10 @@
     </row>
     <row r="740" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A740" s="4" t="s">
-        <v>1190</v>
+        <v>8</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="C740" s="5" t="s">
         <v>1921</v>
@@ -27085,7 +27085,7 @@
     </row>
     <row r="741" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A741" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B741" s="1" t="s">
         <v>1922</v>
@@ -27097,7 +27097,7 @@
     </row>
     <row r="742" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A742" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B742" s="1" t="s">
         <v>1922</v>
@@ -27109,7 +27109,7 @@
     </row>
     <row r="743" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A743" s="4" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B743" s="1" t="s">
         <v>1922</v>
@@ -27121,7 +27121,7 @@
     </row>
     <row r="744" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A744" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B744" s="1" t="s">
         <v>1922</v>
@@ -27133,7 +27133,7 @@
     </row>
     <row r="745" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A745" s="4" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="B745" s="1" t="s">
         <v>1922</v>
@@ -27145,7 +27145,7 @@
     </row>
     <row r="746" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A746" s="4" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B746" s="1" t="s">
         <v>1922</v>
@@ -27157,7 +27157,7 @@
     </row>
     <row r="747" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A747" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B747" s="1" t="s">
         <v>1922</v>
@@ -27169,7 +27169,7 @@
     </row>
     <row r="748" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A748" s="4" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="B748" s="1" t="s">
         <v>1922</v>
@@ -27181,7 +27181,7 @@
     </row>
     <row r="749" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A749" s="4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B749" s="1" t="s">
         <v>1922</v>
@@ -27193,7 +27193,7 @@
     </row>
     <row r="750" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A750" s="4" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="B750" s="1" t="s">
         <v>1922</v>
@@ -27205,7 +27205,7 @@
     </row>
     <row r="751" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A751" s="4" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="B751" s="1" t="s">
         <v>1922</v>
@@ -27217,7 +27217,7 @@
     </row>
     <row r="752" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A752" s="4" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="B752" s="1" t="s">
         <v>1922</v>
@@ -27229,7 +27229,7 @@
     </row>
     <row r="753" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A753" s="4" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="B753" s="1" t="s">
         <v>1922</v>
@@ -27241,7 +27241,7 @@
     </row>
     <row r="754" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A754" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B754" s="1" t="s">
         <v>1922</v>
@@ -27253,7 +27253,7 @@
     </row>
     <row r="755" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A755" s="4" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="B755" s="1" t="s">
         <v>1922</v>
@@ -27265,7 +27265,7 @@
     </row>
     <row r="756" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A756" s="4" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B756" s="1" t="s">
         <v>1922</v>
@@ -27277,7 +27277,7 @@
     </row>
     <row r="757" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A757" s="4" t="s">
-        <v>323</v>
+        <v>426</v>
       </c>
       <c r="B757" s="1" t="s">
         <v>1922</v>
@@ -27289,7 +27289,7 @@
     </row>
     <row r="758" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A758" s="4" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B758" s="1" t="s">
         <v>1922</v>
@@ -27301,7 +27301,7 @@
     </row>
     <row r="759" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A759" s="4" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B759" s="1" t="s">
         <v>1922</v>
@@ -27313,7 +27313,7 @@
     </row>
     <row r="760" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A760" s="4" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="B760" s="1" t="s">
         <v>1922</v>
@@ -27325,7 +27325,7 @@
     </row>
     <row r="761" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A761" s="4" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B761" s="1" t="s">
         <v>1922</v>
@@ -27337,7 +27337,7 @@
     </row>
     <row r="762" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A762" s="4" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B762" s="1" t="s">
         <v>1922</v>
@@ -27349,7 +27349,7 @@
     </row>
     <row r="763" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A763" s="4" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B763" s="1" t="s">
         <v>1922</v>
@@ -27361,7 +27361,7 @@
     </row>
     <row r="764" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A764" s="4" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="B764" s="1" t="s">
         <v>1922</v>
@@ -27373,7 +27373,7 @@
     </row>
     <row r="765" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A765" s="4" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B765" s="1" t="s">
         <v>1922</v>
@@ -27385,7 +27385,7 @@
     </row>
     <row r="766" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A766" s="4" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="B766" s="1" t="s">
         <v>1922</v>
@@ -27397,7 +27397,7 @@
     </row>
     <row r="767" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A767" s="4" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B767" s="1" t="s">
         <v>1922</v>
@@ -27409,7 +27409,7 @@
     </row>
     <row r="768" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A768" s="4" t="s">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="B768" s="1" t="s">
         <v>1922</v>
@@ -27421,7 +27421,7 @@
     </row>
     <row r="769" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A769" s="4" t="s">
-        <v>582</v>
+        <v>629</v>
       </c>
       <c r="B769" s="1" t="s">
         <v>1922</v>
@@ -27433,7 +27433,7 @@
     </row>
     <row r="770" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A770" s="4" t="s">
-        <v>629</v>
+        <v>666</v>
       </c>
       <c r="B770" s="1" t="s">
         <v>1922</v>
@@ -27445,7 +27445,7 @@
     </row>
     <row r="771" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A771" s="4" t="s">
-        <v>666</v>
+        <v>723</v>
       </c>
       <c r="B771" s="1" t="s">
         <v>1922</v>
@@ -27457,7 +27457,7 @@
     </row>
     <row r="772" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A772" s="4" t="s">
-        <v>723</v>
+        <v>1001</v>
       </c>
       <c r="B772" s="1" t="s">
         <v>1922</v>
@@ -27469,7 +27469,7 @@
     </row>
     <row r="773" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A773" s="4" t="s">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="B773" s="1" t="s">
         <v>1922</v>
@@ -27481,7 +27481,7 @@
     </row>
     <row r="774" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A774" s="4" t="s">
-        <v>1026</v>
+        <v>1078</v>
       </c>
       <c r="B774" s="1" t="s">
         <v>1922</v>
@@ -27493,7 +27493,7 @@
     </row>
     <row r="775" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A775" s="4" t="s">
-        <v>1078</v>
+        <v>1103</v>
       </c>
       <c r="B775" s="1" t="s">
         <v>1922</v>
@@ -27505,7 +27505,7 @@
     </row>
     <row r="776" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A776" s="4" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="B776" s="1" t="s">
         <v>1922</v>
@@ -27517,7 +27517,7 @@
     </row>
     <row r="777" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A777" s="4" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="B777" s="1" t="s">
         <v>1922</v>
@@ -27529,7 +27529,7 @@
     </row>
     <row r="778" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A778" s="4" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="B778" s="1" t="s">
         <v>1922</v>
@@ -27541,7 +27541,7 @@
     </row>
     <row r="779" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A779" s="4" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="B779" s="1" t="s">
         <v>1922</v>
@@ -27553,7 +27553,7 @@
     </row>
     <row r="780" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A780" s="4" t="s">
-        <v>1120</v>
+        <v>1133</v>
       </c>
       <c r="B780" s="1" t="s">
         <v>1922</v>
@@ -27565,7 +27565,7 @@
     </row>
     <row r="781" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A781" s="4" t="s">
-        <v>1133</v>
+        <v>1160</v>
       </c>
       <c r="B781" s="1" t="s">
         <v>1922</v>
@@ -27577,7 +27577,7 @@
     </row>
     <row r="782" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A782" s="4" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="B782" s="1" t="s">
         <v>1922</v>
@@ -27589,7 +27589,7 @@
     </row>
     <row r="783" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A783" s="4" t="s">
-        <v>1165</v>
+        <v>1190</v>
       </c>
       <c r="B783" s="1" t="s">
         <v>1922</v>
@@ -27601,7 +27601,7 @@
     </row>
     <row r="784" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A784" s="4" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="B784" s="1" t="s">
         <v>1922</v>
@@ -27613,7 +27613,7 @@
     </row>
     <row r="785" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A785" s="4" t="s">
-        <v>1195</v>
+        <v>1264</v>
       </c>
       <c r="B785" s="1" t="s">
         <v>1922</v>
@@ -27625,7 +27625,7 @@
     </row>
     <row r="786" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A786" s="4" t="s">
-        <v>1264</v>
+        <v>1326</v>
       </c>
       <c r="B786" s="1" t="s">
         <v>1922</v>
@@ -27637,10 +27637,10 @@
     </row>
     <row r="787" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A787" s="4" t="s">
-        <v>1326</v>
+        <v>157</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="C787" s="5" t="s">
         <v>1921</v>
@@ -27649,7 +27649,7 @@
     </row>
     <row r="788" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A788" s="4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B788" s="1" t="s">
         <v>1923</v>
@@ -27661,7 +27661,7 @@
     </row>
     <row r="789" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A789" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B789" s="1" t="s">
         <v>1923</v>
@@ -27673,7 +27673,7 @@
     </row>
     <row r="790" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A790" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B790" s="1" t="s">
         <v>1923</v>
@@ -27685,19 +27685,22 @@
     </row>
     <row r="791" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A791" s="4" t="s">
-        <v>169</v>
+        <v>426</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="C791" s="5" t="s">
         <v>1921</v>
       </c>
+      <c r="E791" s="1" t="s">
+        <v>1925</v>
+      </c>
       <c r="F791" s="5"/>
     </row>
     <row r="792" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A792" s="4" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B792" s="1" t="s">
         <v>1924</v>
@@ -27706,13 +27709,13 @@
         <v>1921</v>
       </c>
       <c r="E792" s="1" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="F792" s="5"/>
     </row>
     <row r="793" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A793" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B793" s="1" t="s">
         <v>1924</v>
@@ -27721,13 +27724,13 @@
         <v>1921</v>
       </c>
       <c r="E793" s="1" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="F793" s="5"/>
     </row>
     <row r="794" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A794" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B794" s="1" t="s">
         <v>1924</v>
@@ -27736,13 +27739,13 @@
         <v>1921</v>
       </c>
       <c r="E794" s="1" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="F794" s="5"/>
     </row>
     <row r="795" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A795" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B795" s="1" t="s">
         <v>1924</v>
@@ -27751,13 +27754,13 @@
         <v>1921</v>
       </c>
       <c r="E795" s="1" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="F795" s="5"/>
     </row>
     <row r="796" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A796" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B796" s="1" t="s">
         <v>1924</v>
@@ -27766,28 +27769,25 @@
         <v>1921</v>
       </c>
       <c r="E796" s="1" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="F796" s="5"/>
     </row>
     <row r="797" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A797" s="4" t="s">
-        <v>447</v>
+        <v>1326</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>1924</v>
+        <v>1329</v>
       </c>
       <c r="C797" s="5" t="s">
         <v>1921</v>
       </c>
-      <c r="E797" s="1" t="s">
-        <v>1930</v>
-      </c>
       <c r="F797" s="5"/>
     </row>
     <row r="798" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A798" s="4" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="B798" s="1" t="s">
         <v>1329</v>
@@ -27799,7 +27799,7 @@
     </row>
     <row r="799" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A799" s="4" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="B799" s="1" t="s">
         <v>1329</v>
@@ -27811,7 +27811,7 @@
     </row>
     <row r="800" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A800" s="4" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="B800" s="1" t="s">
         <v>1329</v>
@@ -27823,19 +27823,22 @@
     </row>
     <row r="801" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A801" s="4" t="s">
-        <v>1339</v>
+        <v>1148</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>1329</v>
+        <v>1931</v>
       </c>
       <c r="C801" s="5" t="s">
-        <v>1921</v>
+        <v>1932</v>
       </c>
       <c r="F801" s="5"/>
+      <c r="G801" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="802" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A802" s="4" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="B802" s="1" t="s">
         <v>1931</v>
@@ -27844,13 +27847,10 @@
         <v>1932</v>
       </c>
       <c r="F802" s="5"/>
-      <c r="G802" s="1" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="803" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A803" s="4" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="B803" s="1" t="s">
         <v>1931</v>
@@ -27859,25 +27859,33 @@
         <v>1932</v>
       </c>
       <c r="F803" s="5"/>
+      <c r="G803" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="804" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A804" s="4" t="s">
-        <v>1156</v>
+        <v>1190</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="C804" s="5" t="s">
         <v>1932</v>
       </c>
-      <c r="F804" s="5"/>
-      <c r="G804" s="1" t="s">
-        <v>13</v>
+      <c r="D804" s="1" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E804" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="F804" s="5" t="s">
+        <v>1718</v>
       </c>
     </row>
     <row r="805" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A805" s="4" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="B805" s="1" t="s">
         <v>1933</v>
@@ -27889,15 +27897,15 @@
         <v>1934</v>
       </c>
       <c r="E805" s="1" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="F805" s="5" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="806" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A806" s="4" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B806" s="1" t="s">
         <v>1933</v>
@@ -27909,15 +27917,15 @@
         <v>1934</v>
       </c>
       <c r="E806" s="1" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="F806" s="5" t="s">
-        <v>1719</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="807" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A807" s="4" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="B807" s="1" t="s">
         <v>1933</v>
@@ -27929,15 +27937,15 @@
         <v>1934</v>
       </c>
       <c r="E807" s="1" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="F807" s="5" t="s">
-        <v>1893</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="808" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A808" s="4" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="B808" s="1" t="s">
         <v>1933</v>
@@ -27949,15 +27957,15 @@
         <v>1934</v>
       </c>
       <c r="E808" s="1" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="F808" s="5" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="809" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A809" s="4" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="B809" s="1" t="s">
         <v>1933</v>
@@ -27969,15 +27977,15 @@
         <v>1934</v>
       </c>
       <c r="E809" s="1" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="F809" s="5" t="s">
-        <v>1941</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="810" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A810" s="4" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="B810" s="1" t="s">
         <v>1933</v>
@@ -27988,33 +27996,25 @@
       <c r="D810" s="1" t="s">
         <v>1934</v>
       </c>
-      <c r="E810" s="1" t="s">
-        <v>1942</v>
-      </c>
       <c r="F810" s="5" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="811" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A811" s="4" t="s">
-        <v>1216</v>
+        <v>538</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>1933</v>
+        <v>1943</v>
       </c>
       <c r="C811" s="5" t="s">
         <v>1932</v>
       </c>
-      <c r="D811" s="1" t="s">
-        <v>1934</v>
-      </c>
-      <c r="F811" s="5" t="s">
-        <v>1791</v>
-      </c>
+      <c r="F811" s="5"/>
     </row>
     <row r="812" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A812" s="4" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B812" s="1" t="s">
         <v>1943</v>
@@ -28026,7 +28026,7 @@
     </row>
     <row r="813" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A813" s="4" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B813" s="1" t="s">
         <v>1943</v>
@@ -28038,7 +28038,7 @@
     </row>
     <row r="814" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A814" s="4" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B814" s="1" t="s">
         <v>1943</v>
@@ -28050,7 +28050,7 @@
     </row>
     <row r="815" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A815" s="4" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B815" s="1" t="s">
         <v>1943</v>
@@ -28062,7 +28062,7 @@
     </row>
     <row r="816" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A816" s="4" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B816" s="1" t="s">
         <v>1943</v>
@@ -28074,7 +28074,7 @@
     </row>
     <row r="817" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A817" s="4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B817" s="1" t="s">
         <v>1943</v>
@@ -28086,10 +28086,10 @@
     </row>
     <row r="818" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A818" s="4" t="s">
-        <v>562</v>
+        <v>1343</v>
       </c>
       <c r="B818" s="1" t="s">
-        <v>1943</v>
+        <v>1346</v>
       </c>
       <c r="C818" s="5" t="s">
         <v>1932</v>
@@ -28098,7 +28098,7 @@
     </row>
     <row r="819" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A819" s="4" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="B819" s="1" t="s">
         <v>1346</v>
@@ -28110,7 +28110,7 @@
     </row>
     <row r="820" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A820" s="4" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="B820" s="1" t="s">
         <v>1346</v>
@@ -28122,7 +28122,7 @@
     </row>
     <row r="821" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A821" s="4" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="B821" s="1" t="s">
         <v>1346</v>
@@ -28134,10 +28134,10 @@
     </row>
     <row r="822" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A822" s="4" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="B822" s="1" t="s">
-        <v>1346</v>
+        <v>1944</v>
       </c>
       <c r="C822" s="5" t="s">
         <v>1932</v>
@@ -28146,7 +28146,7 @@
     </row>
     <row r="823" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A823" s="4" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="B823" s="1" t="s">
         <v>1944</v>
@@ -28158,19 +28158,19 @@
     </row>
     <row r="824" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A824" s="4" t="s">
-        <v>1364</v>
+        <v>14</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="C824" s="5" t="s">
-        <v>1932</v>
+        <v>1946</v>
       </c>
       <c r="F824" s="5"/>
     </row>
     <row r="825" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A825" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B825" s="1" t="s">
         <v>1945</v>
@@ -28182,7 +28182,7 @@
     </row>
     <row r="826" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A826" s="4" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="B826" s="1" t="s">
         <v>1945</v>
@@ -28194,7 +28194,7 @@
     </row>
     <row r="827" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A827" s="4" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="B827" s="1" t="s">
         <v>1945</v>
@@ -28206,7 +28206,7 @@
     </row>
     <row r="828" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A828" s="4" t="s">
-        <v>197</v>
+        <v>426</v>
       </c>
       <c r="B828" s="1" t="s">
         <v>1945</v>
@@ -28218,7 +28218,7 @@
     </row>
     <row r="829" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A829" s="4" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="B829" s="1" t="s">
         <v>1945</v>
@@ -28230,7 +28230,7 @@
     </row>
     <row r="830" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A830" s="4" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B830" s="1" t="s">
         <v>1945</v>
@@ -28242,7 +28242,7 @@
     </row>
     <row r="831" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A831" s="4" t="s">
-        <v>472</v>
+        <v>1001</v>
       </c>
       <c r="B831" s="1" t="s">
         <v>1945</v>
@@ -28254,7 +28254,7 @@
     </row>
     <row r="832" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A832" s="4" t="s">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="B832" s="1" t="s">
         <v>1945</v>
@@ -28266,7 +28266,7 @@
     </row>
     <row r="833" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A833" s="4" t="s">
-        <v>1026</v>
+        <v>1190</v>
       </c>
       <c r="B833" s="1" t="s">
         <v>1945</v>
@@ -28278,19 +28278,24 @@
     </row>
     <row r="834" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A834" s="4" t="s">
-        <v>1190</v>
+        <v>1103</v>
       </c>
       <c r="B834" s="1" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="C834" s="5" t="s">
         <v>1946</v>
       </c>
-      <c r="F834" s="5"/>
+      <c r="F834" s="5" t="s">
+        <v>1719</v>
+      </c>
+      <c r="G834" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="835" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A835" s="4" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="B835" s="1" t="s">
         <v>1947</v>
@@ -28299,7 +28304,7 @@
         <v>1946</v>
       </c>
       <c r="F835" s="5" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="G835" s="1" t="s">
         <v>13</v>
@@ -28307,7 +28312,7 @@
     </row>
     <row r="836" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A836" s="4" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="B836" s="1" t="s">
         <v>1947</v>
@@ -28316,7 +28321,7 @@
         <v>1946</v>
       </c>
       <c r="F836" s="5" t="s">
-        <v>1718</v>
+        <v>1791</v>
       </c>
       <c r="G836" s="1" t="s">
         <v>13</v>
@@ -28324,7 +28329,7 @@
     </row>
     <row r="837" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A837" s="4" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="B837" s="1" t="s">
         <v>1947</v>
@@ -28333,7 +28338,7 @@
         <v>1946</v>
       </c>
       <c r="F837" s="5" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G837" s="1" t="s">
         <v>13</v>
@@ -28341,24 +28346,19 @@
     </row>
     <row r="838" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A838" s="4" t="s">
-        <v>1120</v>
+        <v>876</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="C838" s="5" t="s">
         <v>1946</v>
       </c>
-      <c r="F838" s="5" t="s">
-        <v>1792</v>
-      </c>
-      <c r="G838" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="F838" s="5"/>
     </row>
     <row r="839" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A839" s="4" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="B839" s="1" t="s">
         <v>1948</v>
@@ -28370,7 +28370,7 @@
     </row>
     <row r="840" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A840" s="4" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="B840" s="1" t="s">
         <v>1948</v>
@@ -28382,10 +28382,10 @@
     </row>
     <row r="841" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A841" s="4" t="s">
-        <v>885</v>
+        <v>14</v>
       </c>
       <c r="B841" s="1" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="C841" s="5" t="s">
         <v>1946</v>
@@ -28394,7 +28394,7 @@
     </row>
     <row r="842" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A842" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B842" s="1" t="s">
         <v>1949</v>
@@ -28406,19 +28406,22 @@
     </row>
     <row r="843" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A843" s="4" t="s">
-        <v>19</v>
+        <v>1360</v>
       </c>
       <c r="B843" s="1" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="C843" s="5" t="s">
         <v>1946</v>
       </c>
       <c r="F843" s="5"/>
+      <c r="G843" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="844" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A844" s="4" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="B844" s="1" t="s">
         <v>1950</v>
@@ -28433,10 +28436,10 @@
     </row>
     <row r="845" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A845" s="4" t="s">
-        <v>1364</v>
+        <v>1160</v>
       </c>
       <c r="B845" s="1" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="C845" s="5" t="s">
         <v>1946</v>
@@ -28448,7 +28451,7 @@
     </row>
     <row r="846" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A846" s="4" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="B846" s="1" t="s">
         <v>1951</v>
@@ -28463,7 +28466,7 @@
     </row>
     <row r="847" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A847" s="4" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="B847" s="1" t="s">
         <v>1951</v>
@@ -28478,7 +28481,7 @@
     </row>
     <row r="848" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A848" s="4" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="B848" s="1" t="s">
         <v>1951</v>
@@ -28487,25 +28490,22 @@
         <v>1946</v>
       </c>
       <c r="F848" s="5"/>
-      <c r="G848" s="1" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="849" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A849" s="4" t="s">
-        <v>1173</v>
+        <v>14</v>
       </c>
       <c r="B849" s="1" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="C849" s="5" t="s">
-        <v>1946</v>
+        <v>1953</v>
       </c>
       <c r="F849" s="5"/>
     </row>
     <row r="850" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A850" s="4" t="s">
-        <v>14</v>
+        <v>426</v>
       </c>
       <c r="B850" s="1" t="s">
         <v>1952</v>
@@ -28517,7 +28517,7 @@
     </row>
     <row r="851" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A851" s="4" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="B851" s="1" t="s">
         <v>1952</v>
@@ -28529,7 +28529,7 @@
     </row>
     <row r="852" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A852" s="4" t="s">
-        <v>502</v>
+        <v>723</v>
       </c>
       <c r="B852" s="1" t="s">
         <v>1952</v>
@@ -28541,7 +28541,7 @@
     </row>
     <row r="853" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A853" s="4" t="s">
-        <v>723</v>
+        <v>1026</v>
       </c>
       <c r="B853" s="1" t="s">
         <v>1952</v>
@@ -28553,7 +28553,7 @@
     </row>
     <row r="854" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A854" s="4" t="s">
-        <v>1026</v>
+        <v>1190</v>
       </c>
       <c r="B854" s="1" t="s">
         <v>1952</v>
@@ -28568,16 +28568,19 @@
         <v>1190</v>
       </c>
       <c r="B855" s="1" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="C855" s="5" t="s">
         <v>1953</v>
       </c>
+      <c r="D855" s="1" t="s">
+        <v>1955</v>
+      </c>
       <c r="F855" s="5"/>
     </row>
     <row r="856" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A856" s="4" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="B856" s="1" t="s">
         <v>1954</v>
@@ -28592,7 +28595,7 @@
     </row>
     <row r="857" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A857" s="4" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B857" s="1" t="s">
         <v>1954</v>
@@ -28607,7 +28610,7 @@
     </row>
     <row r="858" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A858" s="4" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="B858" s="1" t="s">
         <v>1954</v>
@@ -28622,7 +28625,7 @@
     </row>
     <row r="859" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A859" s="4" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="B859" s="1" t="s">
         <v>1954</v>
@@ -28637,22 +28640,22 @@
     </row>
     <row r="860" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A860" s="4" t="s">
-        <v>1207</v>
+        <v>601</v>
       </c>
       <c r="B860" s="1" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="C860" s="5" t="s">
         <v>1953</v>
       </c>
-      <c r="D860" s="1" t="s">
-        <v>1955</v>
-      </c>
       <c r="F860" s="5"/>
+      <c r="G860" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="861" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A861" s="4" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B861" s="1" t="s">
         <v>1956</v>
@@ -28667,7 +28670,7 @@
     </row>
     <row r="862" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A862" s="4" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B862" s="1" t="s">
         <v>1956</v>
@@ -28682,7 +28685,7 @@
     </row>
     <row r="863" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A863" s="4" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B863" s="1" t="s">
         <v>1956</v>
@@ -28697,7 +28700,7 @@
     </row>
     <row r="864" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A864" s="4" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B864" s="1" t="s">
         <v>1956</v>
@@ -28712,7 +28715,7 @@
     </row>
     <row r="865" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A865" s="4" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B865" s="1" t="s">
         <v>1956</v>
@@ -28727,7 +28730,7 @@
     </row>
     <row r="866" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A866" s="4" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B866" s="1" t="s">
         <v>1956</v>
@@ -28742,7 +28745,7 @@
     </row>
     <row r="867" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A867" s="4" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B867" s="1" t="s">
         <v>1956</v>
@@ -28757,22 +28760,24 @@
     </row>
     <row r="868" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A868" s="4" t="s">
-        <v>626</v>
+        <v>1026</v>
       </c>
       <c r="B868" s="1" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="C868" s="5" t="s">
-        <v>1953</v>
-      </c>
-      <c r="F868" s="5"/>
+        <v>1958</v>
+      </c>
+      <c r="F868" s="5" t="s">
+        <v>1719</v>
+      </c>
       <c r="G868" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="869" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A869" s="4" t="s">
-        <v>1026</v>
+        <v>1093</v>
       </c>
       <c r="B869" s="1" t="s">
         <v>1957</v>
@@ -28780,8 +28785,11 @@
       <c r="C869" s="5" t="s">
         <v>1958</v>
       </c>
+      <c r="E869" s="1" t="s">
+        <v>1959</v>
+      </c>
       <c r="F869" s="5" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="G869" s="1" t="s">
         <v>13</v>
@@ -28789,7 +28797,7 @@
     </row>
     <row r="870" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A870" s="4" t="s">
-        <v>1093</v>
+        <v>1176</v>
       </c>
       <c r="B870" s="1" t="s">
         <v>1957</v>
@@ -28797,30 +28805,13 @@
       <c r="C870" s="5" t="s">
         <v>1958</v>
       </c>
-      <c r="E870" s="1" t="s">
-        <v>1959</v>
-      </c>
-      <c r="F870" s="5" t="s">
-        <v>1718</v>
-      </c>
+      <c r="F870" s="5"/>
       <c r="G870" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="871" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A871" s="4" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B871" s="1" t="s">
-        <v>1957</v>
-      </c>
-      <c r="C871" s="5" t="s">
-        <v>1958</v>
-      </c>
-      <c r="F871" s="5"/>
-      <c r="G871" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A871" s="6"/>
     </row>
     <row r="872" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A872" s="6"/>
@@ -31819,17 +31810,15 @@
     <row r="1870" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1870" s="6"/>
     </row>
-    <row r="1871" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1871" s="6"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:G871"/>
+  <autoFilter ref="A1:G870"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G1870" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G1869" type="list">
       <formula1>"yes"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Cet identifiant n'existe pas dans la feuille Personnages." errorStyle="warning" errorTitle="Personnage inconnu" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A1871" type="list">
+    <dataValidation allowBlank="true" error="Cet identifiant n'existe pas dans la feuille Personnages." errorStyle="warning" errorTitle="Personnage inconnu" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A1870" type="list">
       <formula1>Personnages!$A$2:$A$1784</formula1>
       <formula2>0</formula2>
     </dataValidation>
